--- a/光伏配储项目/电价数据/2026/沟美站.xlsx
+++ b/光伏配储项目/电价数据/2026/沟美站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.35324</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.86482</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40977</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.42164</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08431</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.8176599999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.48492</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.49807</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6097</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7606900000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.16818</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.62955</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6814199999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9264600000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5418500000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.23645</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39579</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.12498</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.14074</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.35235</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.45496</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.47513</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.73866</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7936299999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.24724</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95987</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.95272</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.82216</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7897999999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5328099999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50783</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.44061</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.77125</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9541000000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.05273</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.56032</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.55089</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.53049</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.24493</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.48599</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.54277</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5435</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.72546</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.68947</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.92714</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.84665</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5601499999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.47414</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.42561</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.72199</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.03797</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6417200000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8408600000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.91465</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.25083</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.7063</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18397</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.92438</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.28048</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16587</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.35158</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08294</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15047</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7066699999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.0456</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.96278</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.02827</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.90151</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.14561</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.96348</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9144099999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9740700000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46344</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45738</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33693</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5221399999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53059</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.47763</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.51196</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.46383</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.12359</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.16304</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27027</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.0818</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.01059</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7968</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.78035</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.00729</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.99822</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.96745</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9712499999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.96797</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.95472</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.90923</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8862899999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.07873</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.57267</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.65462</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.85725</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.87638</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.72948</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7899400000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.54977</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.97299</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.48735</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45532</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52083</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53144</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.61468</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.66612</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6762699999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.67843</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.43171</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6494800000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47741</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6676</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8406</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.81041</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.97587</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48031</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.67848</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.46385</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.66191</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.86441</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.60322</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.00623</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.64283</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.59145</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.73153</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44842</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47001</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34468</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.52935</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.46464</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47727</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52904</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.67999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45568</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.69009</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.68306</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5816</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.47706</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.48436</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.74675</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.53701</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.56879</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.49266</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6260800000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7440099999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.53665</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65511</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.57311</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.54404</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50278</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.48624</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45991</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.35575</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14263</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24737</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11349</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.06511</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.47397</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31479</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.22611</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.23455</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18134</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.17538</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.18784</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20623</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18339</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16349</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24271</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19107</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09564</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00974</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20569</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04901</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19796</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05983</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05804</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31436</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.43917</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43381</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44553</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48563</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78816</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87024</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6486000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5702699999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45885</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59356</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6340800000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9648600000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.65243</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9037200000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.38814</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6673300000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.16967</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25898</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32138</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.8765599999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.56843</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.4983399999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.45811</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.5204</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5229199999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.36116</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.05424</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.48722</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.88544</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.07871</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.82962</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.57392</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.6458200000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.50893</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.54088</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.47998</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.45381</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.46557</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.54198</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.49062</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5200499999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.19654</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1754</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.01986</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.49661</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6611399999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30368</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.18516</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.20298</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17687</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.19739</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17422</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26116</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.18832</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.18495</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.23193</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.23638</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.19374</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17026</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29683</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.17749</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26856</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2840299999999999</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28677</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27637</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29845</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28489</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30069</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.16264</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6940599999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50417</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4827</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44737</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.5120800000000001</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38885</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.57296</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25902</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.74412</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.55947</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42195</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43228</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.47807</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.71669</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50126</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47484</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7370599999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.25168</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48584</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24569</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.21263</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18653</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.17926</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26975</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27053</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26964</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18094</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1784</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1395</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17813</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18394</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.23059</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.15157</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14357</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20916</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.25414</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24564</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26571</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.22546</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22487</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31751</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.04770000000000001</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26726</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29992</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.62309</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5159600000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19038</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29273</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48786</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.65504</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61287</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6597499999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8131</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4997200000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.44706</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31044</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26782</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48786</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.52846</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56909</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6835800000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.82726</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.53522</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7353099999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.58945</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30298</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27752</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.03465</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26758</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40772</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.23782</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.26421</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.24902</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.18617</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.19329</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.19406</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.23109</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.18642</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.15128</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.03589</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.03742</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.03659</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.15155</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18765</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15031</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.03601</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.14367</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.14618</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.03587</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.03591</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16131</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13469</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27196</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00309</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24063</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.27383</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20614</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.23686</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23388</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25112</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.17685</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25116</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16087</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.16614</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.24519</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22085</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.28095</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.2672</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17259</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.16979</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.25963</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.18733</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21054</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20146</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.00687</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18182</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24053</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.00417</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16691</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02212</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03441</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00313</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03461</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21309</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27265</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27595</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25822</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14282</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.13931</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.14326</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14095</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.13741</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.12761</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.16476</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21294</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.22211</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8540599999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86317</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08537</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23958</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28472</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.64438</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00211</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.07004000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.58341</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74637</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.95639</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.5915499999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8152999999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.81353</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.81778</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.91561</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.2982</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.46708</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.24979</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.16277</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.23967</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23372</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.19739</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22209</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18177</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14171</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.13684</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.13925</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.12628</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.15477</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.20911</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.25184</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22129</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.22926</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24149</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28238</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5691499999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46034</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.10495</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82585</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8140299999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54208</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6629299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.87309</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5488099999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.30953</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51658</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.51847</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.08946</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.82364</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5478500000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.70851</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.47673</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.57398</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.51159</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.68463</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6364099999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.04412</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.84426</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.72168</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58397</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31418</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27046</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52366</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.48926</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.50531</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.45272</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5445399999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45869</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.55467</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31762</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.69682</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.25994</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.49484</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.47032</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.50981</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44617</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33318</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33654</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14584</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19877</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04854</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12217</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14606</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18662</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22696</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16391</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20674</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16754</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.48083</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.64477</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.45278</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.45721</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.51911</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.52579</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.50873</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.48759</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49093</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3649</v>
       </c>
     </row>
   </sheetData>
